--- a/output/iter_3/oa_results.xlsx
+++ b/output/iter_3/oa_results.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="452" uniqueCount="452">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="254" uniqueCount="254">
   <si>
     <t xml:space="preserve">count</t>
   </si>
@@ -32,60 +32,60 @@
     <t xml:space="preserve">oa</t>
   </si>
   <si>
-    <t xml:space="preserve">https://openalex.org/works?page=1&amp;filter=title_and_abstract.search%3A%28%22Pygoscelis%20adeliae%22%20OR%20%22Pygoscelis%20papua%22%20OR%20%22Pygoscelis%20antarctica%22%20OR%20%22Pygoscelis%20antarcticus%22%20OR%20%22Aptenodytes%20forsteri%22%20OR%20%22adelie%20penguin%22%20OR%20%22Ad%C3%A9lie%20penguin%22%20OR%20%22gentoo%20penguin%22%20OR%20%22Gentoo%20penguin%22%20OR%20%22Chinstrap%20penguin%22%20OR%20%22emperor%20penguin%22%20OR%20%22Pygoscelis%22%20OR%20%22Aptenodytes%22%20OR%20%22penguin%22%20OR%20%22adeliae%22%20OR%20%22papua%22%20OR%20%22antarctica%22%20OR%20%22antarcticus%22%20OR%20%22forsteri%22%20OR%20%22adelie%22%20OR%20%22Ad%C3%A9lie%22%20OR%20%22gentoo%22%20OR%20%22Gentoo%22%20OR%20%22emperor%22%29%20AND%20%28%22Antarctic%20Peninsula%20region%22%20OR%20%22Western%20Antarctic%20Peninsula%22%20OR%20%22South%20Shetland%20Islands%22%20OR%20%22South%20Orkney%20ISland%22%20OR%20%22Brandsfield%20strait%22%20OR%20%22Gerlache%20Strait%22%20OR%20%22Marguerite%20Bay%22%20OR%20%22Antarctic%20Sound%22%20OR%20%22CEMP%20site%22%20OR%20%22domain%201%22%20OR%20%22Western%20Antarctic%20Peninsula-Southscotia%20arc%22%20OR%20%22ccamlr%20subarea%22%20OR%20%22ccamlr%20region%22%20OR%20%22ccamlr%20region%2048.1%22%20OR%20%22ccamlr%20region%2048.2%22%20OR%20%22ccamlr%20region%2088.3%22%20OR%20%22ccamlr%20subarea%2048.1%22%20OR%20%22ccamlr%20subarea%2048.2%22%20OR%20%22ccamlr%20subarea%2088.3%22%29&amp;id=iAroPbyBSFEzsahky8Djkphttps://openalex.org/works?page=1&amp;filter=title_and_abstract.search%3A%28%22Pygoscelis%20adeliae%22%20OR%20%22Pygoscelis%20papua%22%20OR%20%22Pygoscelis%20antarctica%22%20OR%20%22Pygoscelis%20antarcticus%22%20OR%20%22Aptenodytes%20forsteri%22%20OR%20%22Pygoscelis%22%20OR%20%22Aptenodytes%22%20OR%20%22penguin%22%20OR%20%22adeliae%22%20OR%20%22papua%22%20OR%20%22antarctica%22%20OR%20%22antarcticus%22%20OR%20%22forsteri%22%20OR%20%22adelie%22%20OR%20%22Ad%C3%A9lie%22%20OR%20%22gentoo%22%20OR%20%22Chinstrap%22%20OR%20%22emperor%22%29%20AND%20%28%22Antarctic%20Peninsula%22%20OR%20%22South%20Shetland%20Islands%22%20OR%20%22South%20Orkney%20Island%22%20OR%20%22Brandsfield%20strait%22%20OR%20%22Gerlache%20Strait%22%20OR%20%22Marguerite%20Bay%22%20OR%20%22Antarctic%20Sound%22%20OR%20%22CEMP%20site%22%20OR%20%22domain%201%22%20OR%20%22subarea%2048.1%22%20OR%20%22subarea%2048.2%22%20OR%20%22subarea%2088.3%22%20OR%20%22area%2048%22%20OR%20%2248.1%22%20OR%20%2248.2%22%20OR%20%2288.3%22%20OR%20%22small-scale%20management%20unit%22%20OR%20%22ccamlr%22%29%20AND%20%28%22monitoring%22%20OR%20%22survey%22%20OR%20%22inventory%22%20OR%20%22census%22%20OR%20%22study%22%20OR%20%22Time-series%22%20OR%20%22Time%20series%22%20OR%20%22Monitor%22%20OR%20%22data%20collection%22%20OR%20%22Antarctic%20Site%20Inventory%22%20OR%20%22long%20term%22%20OR%20%22trend%22%20OR%20%22change%22%20OR%20%22seasonal%22%20OR%20%22season%22%20OR%20%22years%22%20OR%20%22decadal%22%20OR%20%22decades%22%20OR%20%22interannual%22%20OR%20%22monitored%22%20OR%20%22counts%22%20OR%20%22observation%22%29&amp;id=9RPnEewibdWWQ8tsu3W2b7</t>
+    <t xml:space="preserve">https://openalex.org/works?page=1&amp;filter=title_and_abstract.search%3A%28%22Pygoscelis%20adeliae%22%20OR%20%22Pygoscelis%20papua%22%20OR%20%22Pygoscelis%20antarctica%22%20OR%20%22Pygoscelis%20antarcticus%22%20OR%20%22Aptenodytes%20forsteri%22%20OR%20%22Pygoscelis%22%20OR%20%22Aptenodytes%22%20OR%20%22penguin%22%20OR%20%22adeliae%22%20OR%20%22papua%22%20OR%20%22antarcticus%22%20OR%20%22forsteri%22%20OR%20%22adelie%22%20OR%20%22Ad%C3%A9lie%22%20OR%20%22gentoo%22%20OR%20%22Chinstrap%22%20OR%20%22emperor%22%29%20AND%20%28%22Antarctic%20Peninsula%22%20OR%20%22South%20Shetland%20Islands%22%20OR%20%22South%20Orkney%20Island%22%20OR%20%22Brandsfield%20strait%22%20OR%20%22Gerlache%20Strait%22%20OR%20%22Marguerite%20Bay%22%20OR%20%22Antarctic%20Sound%22%20OR%20%22CEMP%20site%22%20OR%20%22domain%201%22%20OR%20%22subarea%2048.1%22%20OR%20%22subarea%2048.2%22%20OR%20%22subarea%2088.3%22%20OR%20%22area%2048%22%20OR%20%2248.1%22%20OR%20%2248.2%22%20OR%20%2288.3%22%20OR%20%22small-scale%20management%20unit%22%20OR%20%22ccamlr%22%29%20AND%20%28%22monitoring%22%20OR%20%22survey%22%20OR%20%22inventory%22%20OR%20%22census%22%20OR%20%22study%22%20OR%20%22Time-series%22%20OR%20%22Time%20series%22%20OR%20%22Monitor%22%20OR%20%22data%20collection%22%20OR%20%22Antarctic%20Site%20Inventory%22%20OR%20%22long%20term%22%20OR%20%22trend%22%20OR%20%22change%22%20OR%20%22seasonal%22%20OR%20%22season%22%20OR%20%22years%22%20OR%20%22decadal%22%20OR%20%22decades%22%20OR%20%22interannual%22%20OR%20%22monitored%22%20OR%20%22counts%22%20OR%20%22observation%22%29&amp;id=2iytNJ1sKMwuJATY13C9sj</t>
   </si>
   <si>
     <t xml:space="preserve">key_display_name</t>
   </si>
   <si>
+    <t xml:space="preserve">dataset</t>
+  </si>
+  <si>
     <t xml:space="preserve">article</t>
   </si>
   <si>
-    <t xml:space="preserve">dataset</t>
-  </si>
-  <si>
     <t xml:space="preserve">preprint</t>
   </si>
   <si>
+    <t xml:space="preserve">dissertation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">book-chapter</t>
+  </si>
+  <si>
     <t xml:space="preserve">peer-review</t>
   </si>
   <si>
-    <t xml:space="preserve">dissertation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">book-chapter</t>
-  </si>
-  <si>
     <t xml:space="preserve">book</t>
   </si>
   <si>
     <t xml:space="preserve">review</t>
   </si>
   <si>
+    <t xml:space="preserve">paratext</t>
+  </si>
+  <si>
+    <t xml:space="preserve">letter</t>
+  </si>
+  <si>
+    <t xml:space="preserve">editorial</t>
+  </si>
+  <si>
+    <t xml:space="preserve">erratum</t>
+  </si>
+  <si>
+    <t xml:space="preserve">other</t>
+  </si>
+  <si>
+    <t xml:space="preserve">libguides</t>
+  </si>
+  <si>
+    <t xml:space="preserve">reference-entry</t>
+  </si>
+  <si>
     <t xml:space="preserve">report</t>
   </si>
   <si>
-    <t xml:space="preserve">paratext</t>
-  </si>
-  <si>
-    <t xml:space="preserve">letter</t>
-  </si>
-  <si>
-    <t xml:space="preserve">other</t>
-  </si>
-  <si>
-    <t xml:space="preserve">editorial</t>
-  </si>
-  <si>
-    <t xml:space="preserve">erratum</t>
-  </si>
-  <si>
-    <t xml:space="preserve">libguides</t>
-  </si>
-  <si>
-    <t xml:space="preserve">reference-entry</t>
-  </si>
-  <si>
     <t xml:space="preserve">standard</t>
   </si>
   <si>
@@ -98,27 +98,24 @@
     <t xml:space="preserve">retraction</t>
   </si>
   <si>
+    <t xml:space="preserve">repository</t>
+  </si>
+  <si>
     <t xml:space="preserve">journal</t>
   </si>
   <si>
-    <t xml:space="preserve">repository</t>
-  </si>
-  <si>
     <t xml:space="preserve">ebook platform</t>
   </si>
   <si>
+    <t xml:space="preserve">book series</t>
+  </si>
+  <si>
     <t xml:space="preserve">conference</t>
   </si>
   <si>
-    <t xml:space="preserve">book series</t>
-  </si>
-  <si>
     <t xml:space="preserve">Geological and Geochemical Analysis</t>
   </si>
   <si>
-    <t xml:space="preserve">Soil Carbon and Nitrogen Dynamics</t>
-  </si>
-  <si>
     <t xml:space="preserve">Ecology and Vegetation Dynamics Studies</t>
   </si>
   <si>
@@ -131,9 +128,6 @@
     <t xml:space="preserve">Genetic diversity and population structure</t>
   </si>
   <si>
-    <t xml:space="preserve">Plant Stress Responses and Tolerance</t>
-  </si>
-  <si>
     <t xml:space="preserve">Genomics and Phylogenetic Studies</t>
   </si>
   <si>
@@ -146,45 +140,24 @@
     <t xml:space="preserve">Marine and coastal ecosystems</t>
   </si>
   <si>
-    <t xml:space="preserve">Diverse Aspects of Tourism Research</t>
-  </si>
-  <si>
     <t xml:space="preserve">Gut microbiota and health</t>
   </si>
   <si>
     <t xml:space="preserve">Atmospheric chemistry and aerosols</t>
   </si>
   <si>
-    <t xml:space="preserve">Plant-Microbe Interactions and Immunity</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Archaeology and ancient environmental studies</t>
-  </si>
-  <si>
     <t xml:space="preserve">Avian ecology and behavior</t>
   </si>
   <si>
     <t xml:space="preserve">Malaria Research and Control</t>
   </si>
   <si>
-    <t xml:space="preserve">scientometrics and bibliometrics research</t>
-  </si>
-  <si>
     <t xml:space="preserve">Paleontology and Stratigraphy of Fossils</t>
   </si>
   <si>
     <t xml:space="preserve">earthquake and tectonic studies</t>
   </si>
   <si>
-    <t xml:space="preserve">Remote Sensing in Agriculture</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dental materials and restorations</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SARS-CoV-2 and COVID-19 Research</t>
-  </si>
-  <si>
     <t xml:space="preserve">Toxic Organic Pollutants Impact</t>
   </si>
   <si>
@@ -215,27 +188,15 @@
     <t xml:space="preserve">Animal Behavior and Reproduction</t>
   </si>
   <si>
-    <t xml:space="preserve">Plant Molecular Biology Research</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Air Quality and Health Impacts</t>
-  </si>
-  <si>
     <t xml:space="preserve">Robotics and Sensor-Based Localization</t>
   </si>
   <si>
-    <t xml:space="preserve">Antimicrobial Resistance in Staphylococcus</t>
-  </si>
-  <si>
     <t xml:space="preserve">Wildlife Ecology and Conservation</t>
   </si>
   <si>
     <t xml:space="preserve">Global Maternal and Child Health</t>
   </si>
   <si>
-    <t xml:space="preserve">Land Use and Ecosystem Services</t>
-  </si>
-  <si>
     <t xml:space="preserve">Marine and fisheries research</t>
   </si>
   <si>
@@ -251,21 +212,12 @@
     <t xml:space="preserve">Glaucoma and retinal disorders</t>
   </si>
   <si>
-    <t xml:space="preserve">Solar and Space Plasma Dynamics</t>
-  </si>
-  <si>
     <t xml:space="preserve">Microbial Natural Products and Biosynthesis</t>
   </si>
   <si>
     <t xml:space="preserve">Oceanographic and Atmospheric Processes</t>
   </si>
   <si>
-    <t xml:space="preserve">Plant Water Relations and Carbon Dynamics</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Seismic Imaging and Inversion Techniques</t>
-  </si>
-  <si>
     <t xml:space="preserve">Venous Thromboembolism Diagnosis and Management</t>
   </si>
   <si>
@@ -278,54 +230,15 @@
     <t xml:space="preserve">Fish Ecology and Management Studies</t>
   </si>
   <si>
-    <t xml:space="preserve">Photosynthetic Processes and Mechanisms</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Microbial bioremediation and biosurfactants</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Astro and Planetary Science</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Hydrology and Watershed Management Studies</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Amphibian and Reptile Biology</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Meat and Animal Product Quality</t>
-  </si>
-  <si>
     <t xml:space="preserve">Coral and Marine Ecosystems Studies</t>
   </si>
   <si>
-    <t xml:space="preserve">Atmospheric aerosols and clouds</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Liver Disease Diagnosis and Treatment</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Plant Diversity and Evolution</t>
-  </si>
-  <si>
     <t xml:space="preserve">Healthcare Policy and Management</t>
   </si>
   <si>
-    <t xml:space="preserve">Groundwater and Isotope Geochemistry</t>
-  </si>
-  <si>
     <t xml:space="preserve">Hydrocarbon exploration and reservoir analysis</t>
   </si>
   <si>
-    <t xml:space="preserve">Enzyme Immobilization Techniques</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Advanced Polymer Synthesis and Characterization</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Planetary Science and Exploration</t>
-  </si>
-  <si>
     <t xml:space="preserve">COVID-19 epidemiological studies</t>
   </si>
   <si>
@@ -338,33 +251,15 @@
     <t xml:space="preserve">Pleistocene-Era Hominins and Archaeology</t>
   </si>
   <si>
-    <t xml:space="preserve">Neurobiology and Insect Physiology Research</t>
-  </si>
-  <si>
     <t xml:space="preserve">Child Abuse and Trauma</t>
   </si>
   <si>
-    <t xml:space="preserve">Ethnobotanical and Medicinal Plants Studies</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Chromosomal and Genetic Variations</t>
-  </si>
-  <si>
     <t xml:space="preserve">Environmental Toxicology and Ecotoxicology</t>
   </si>
   <si>
     <t xml:space="preserve">Aquaculture Nutrition and Growth</t>
   </si>
   <si>
-    <t xml:space="preserve">Mycorrhizal Fungi and Plant Interactions</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Meteorological Phenomena and Simulations</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Algal biology and biofuel production</t>
-  </si>
-  <si>
     <t xml:space="preserve">Salmonella and Campylobacter epidemiology</t>
   </si>
   <si>
@@ -377,36 +272,24 @@
     <t xml:space="preserve">Aquaculture disease management and microbiota</t>
   </si>
   <si>
-    <t xml:space="preserve">Structural Health Monitoring Techniques</t>
-  </si>
-  <si>
     <t xml:space="preserve">Landslides and related hazards</t>
   </si>
   <si>
     <t xml:space="preserve">Colorectal Cancer Screening and Detection</t>
   </si>
   <si>
-    <t xml:space="preserve">Fire effects on ecosystems</t>
-  </si>
-  <si>
     <t xml:space="preserve">Global Cancer Incidence and Screening</t>
   </si>
   <si>
     <t xml:space="preserve">Corneal surgery and disorders</t>
   </si>
   <si>
-    <t xml:space="preserve">Geophysical and Geoelectrical Methods</t>
-  </si>
-  <si>
     <t xml:space="preserve">Family Dynamics and Relationships</t>
   </si>
   <si>
     <t xml:space="preserve">Genetic and phenotypic traits in livestock</t>
   </si>
   <si>
-    <t xml:space="preserve">RNA Research and Splicing</t>
-  </si>
-  <si>
     <t xml:space="preserve">Virus-based gene therapy research</t>
   </si>
   <si>
@@ -419,45 +302,27 @@
     <t xml:space="preserve">Cryospheric studies and observations</t>
   </si>
   <si>
-    <t xml:space="preserve">Coastal and Marine Dynamics</t>
-  </si>
-  <si>
     <t xml:space="preserve">GNSS positioning and interference</t>
   </si>
   <si>
     <t xml:space="preserve">Marine animal studies overview</t>
   </si>
   <si>
-    <t xml:space="preserve">biodegradable polymer synthesis and properties</t>
-  </si>
-  <si>
     <t xml:space="preserve">Genetics, Aging, and Longevity in Model Organisms</t>
   </si>
   <si>
-    <t xml:space="preserve">Wind Energy Research and Development</t>
-  </si>
-  <si>
     <t xml:space="preserve">Effects and risks of endocrine disrupting chemicals</t>
   </si>
   <si>
-    <t xml:space="preserve">Remote-Sensing Image Classification</t>
-  </si>
-  <si>
     <t xml:space="preserve">Parasites and Host Interactions</t>
   </si>
   <si>
     <t xml:space="preserve">Insect and Arachnid Ecology and Behavior</t>
   </si>
   <si>
-    <t xml:space="preserve">Forensic and Genetic Research</t>
-  </si>
-  <si>
     <t xml:space="preserve">Microplastics and Plastic Pollution</t>
   </si>
   <si>
-    <t xml:space="preserve">Geographic Information Systems Studies</t>
-  </si>
-  <si>
     <t xml:space="preserve">Migration, Health and Trauma</t>
   </si>
   <si>
@@ -467,24 +332,12 @@
     <t xml:space="preserve">Soil Geostatistics and Mapping</t>
   </si>
   <si>
-    <t xml:space="preserve">Coastal wetland ecosystem dynamics</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Lightning and Electromagnetic Phenomena</t>
-  </si>
-  <si>
     <t xml:space="preserve">Heavy Metal Exposure and Toxicity</t>
   </si>
   <si>
-    <t xml:space="preserve">Synthetic Aperture Radar (SAR) Applications and Techniques</t>
-  </si>
-  <si>
     <t xml:space="preserve">Parasite Biology and Host Interactions</t>
   </si>
   <si>
-    <t xml:space="preserve">Astrophysics and Cosmic Phenomena</t>
-  </si>
-  <si>
     <t xml:space="preserve">Mercury impact and mitigation studies</t>
   </si>
   <si>
@@ -503,63 +356,33 @@
     <t xml:space="preserve">Nutritional Studies and Diet</t>
   </si>
   <si>
-    <t xml:space="preserve">Polysaccharides and Plant Cell Walls</t>
-  </si>
-  <si>
     <t xml:space="preserve">Blood Coagulation and Thrombosis Mechanisms</t>
   </si>
   <si>
-    <t xml:space="preserve">Drilling and Well Engineering</t>
-  </si>
-  <si>
     <t xml:space="preserve">Species Distribution and Climate Change</t>
   </si>
   <si>
-    <t xml:space="preserve">Metabolic Engineering and Synthetic Biology</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Heat shock proteins research</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Radioactivity and Radon Measurements</t>
-  </si>
-  <si>
     <t xml:space="preserve">Paleontology and Evolutionary Biology</t>
   </si>
   <si>
     <t xml:space="preserve">Geological formations and processes</t>
   </si>
   <si>
-    <t xml:space="preserve">Team Dynamics and Performance</t>
-  </si>
-  <si>
     <t xml:space="preserve">Viral gastroenteritis research and epidemiology</t>
   </si>
   <si>
     <t xml:space="preserve">Methane Hydrates and Related Phenomena</t>
   </si>
   <si>
-    <t xml:space="preserve">Indoor Air Quality and Microbial Exposure</t>
-  </si>
-  <si>
     <t xml:space="preserve">Crustacean biology and ecology</t>
   </si>
   <si>
-    <t xml:space="preserve">Skin Protection and Aging</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Fungal Infections and Studies</t>
-  </si>
-  <si>
     <t xml:space="preserve">Bacteriophages and microbial interactions</t>
   </si>
   <si>
     <t xml:space="preserve">Physiological and biochemical adaptations</t>
   </si>
   <si>
-    <t xml:space="preserve">Ocean Waves and Remote Sensing</t>
-  </si>
-  <si>
     <t xml:space="preserve">Insect Pest Control Strategies</t>
   </si>
   <si>
@@ -569,30 +392,12 @@
     <t xml:space="preserve">Marine Bivalve and Aquaculture Studies</t>
   </si>
   <si>
-    <t xml:space="preserve">Radioactive contamination and transfer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dark Matter and Cosmic Phenomena</t>
-  </si>
-  <si>
     <t xml:space="preserve">Emergency and Acute Care Studies</t>
   </si>
   <si>
-    <t xml:space="preserve">Seed Germination and Physiology</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Data Management and Algorithms</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Spectroscopy and Laser Applications</t>
-  </si>
-  <si>
     <t xml:space="preserve">Virology and Viral Diseases</t>
   </si>
   <si>
-    <t xml:space="preserve">Streptococcal Infections and Treatments</t>
-  </si>
-  <si>
     <t xml:space="preserve">Parasitic infections in humans and animals</t>
   </si>
   <si>
@@ -602,45 +407,15 @@
     <t xml:space="preserve">Remote Sensing and LiDAR Applications</t>
   </si>
   <si>
-    <t xml:space="preserve">Nematode management and characterization studies</t>
-  </si>
-  <si>
     <t xml:space="preserve">Advanced Data Storage Technologies</t>
   </si>
   <si>
     <t xml:space="preserve">Underwater Vehicles and Communication Systems</t>
   </si>
   <si>
-    <t xml:space="preserve">3D Surveying and Cultural Heritage</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Precipitation Measurement and Analysis</t>
-  </si>
-  <si>
     <t xml:space="preserve">Respiratory viral infections research</t>
   </si>
   <si>
-    <t xml:space="preserve">Climate Change and Health Impacts</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Plant nutrient uptake and metabolism</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Light effects on plants</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Solar Radiation and Photovoltaics</t>
-  </si>
-  <si>
-    <t xml:space="preserve">COVID-19 and healthcare impacts</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Soil Moisture and Remote Sensing</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Atmospheric Ozone and Climate</t>
-  </si>
-  <si>
     <t xml:space="preserve">Climate change and permafrost</t>
   </si>
   <si>
@@ -656,12 +431,6 @@
     <t xml:space="preserve">Ichthyology and Marine Biology</t>
   </si>
   <si>
-    <t xml:space="preserve">Seaweed-derived Bioactive Compounds</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Biosensors and Analytical Detection</t>
-  </si>
-  <si>
     <t xml:space="preserve">Geophysics and Gravity Measurements</t>
   </si>
   <si>
@@ -674,24 +443,12 @@
     <t xml:space="preserve">Trauma and Emergency Care Studies</t>
   </si>
   <si>
-    <t xml:space="preserve">Legume Nitrogen Fixing Symbiosis</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tropical and Extratropical Cyclones Research</t>
-  </si>
-  <si>
     <t xml:space="preserve">Climate Change Communication and Perception</t>
   </si>
   <si>
-    <t xml:space="preserve">Water Treatment and Disinfection</t>
-  </si>
-  <si>
     <t xml:space="preserve">Viral Diseases in Livestock and Poultry</t>
   </si>
   <si>
-    <t xml:space="preserve">Reproductive biology and impacts on aquatic species</t>
-  </si>
-  <si>
     <t xml:space="preserve">Reproductive System and Pregnancy</t>
   </si>
   <si>
@@ -704,42 +461,18 @@
     <t xml:space="preserve">Sesquiterpenes and Asteraceae Studies</t>
   </si>
   <si>
-    <t xml:space="preserve">Synthetic Organic Chemistry Methods</t>
-  </si>
-  <si>
     <t xml:space="preserve">Animal Disease Management and Epidemiology</t>
   </si>
   <si>
-    <t xml:space="preserve">Facial Trauma and Fracture Management</t>
-  </si>
-  <si>
     <t xml:space="preserve">Plant Pathogenic Bacteria Studies</t>
   </si>
   <si>
-    <t xml:space="preserve">Cardiovascular and Diving-Related Complications</t>
-  </si>
-  <si>
     <t xml:space="preserve">Viral Infections and Outbreaks Research</t>
   </si>
   <si>
     <t xml:space="preserve">Atmospheric and Environmental Gas Dynamics</t>
   </si>
   <si>
-    <t xml:space="preserve">Tree-ring climate responses</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Distributed Constraint Optimization Problems and Algorithms</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Geophysical Methods and Applications</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Enzyme Production and Characterization</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Maritime Navigation and Safety</t>
-  </si>
-  <si>
     <t xml:space="preserve">Birth, Development, and Health</t>
   </si>
   <si>
@@ -758,33 +491,9 @@
     <t xml:space="preserve">Microbial infections and disease research</t>
   </si>
   <si>
-    <t xml:space="preserve">Forest Insect Ecology and Management</t>
-  </si>
-  <si>
     <t xml:space="preserve">Underwater Acoustics Research</t>
   </si>
   <si>
-    <t xml:space="preserve">Biomedical Text Mining and Ontologies</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Assisted Reproductive Technology and Twin Pregnancy</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Geochemistry and Elemental Analysis</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SARS-CoV-2 detection and testing</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Seismic Waves and Analysis</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Plant responses to elevated CO2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Evolution and Genetic Dynamics</t>
-  </si>
-  <si>
     <t xml:space="preserve">Geomagnetism and Paleomagnetism Studies</t>
   </si>
   <si>
@@ -797,48 +506,27 @@
     <t xml:space="preserve">Intellectual Capital and Performance Analysis</t>
   </si>
   <si>
-    <t xml:space="preserve">Clay minerals and soil interactions</t>
-  </si>
-  <si>
     <t xml:space="preserve">Perfluoroalkyl and Polyfluoroalkyl Substances in the Environment</t>
   </si>
   <si>
     <t xml:space="preserve">Protist diversity and phylogeny</t>
   </si>
   <si>
-    <t xml:space="preserve">Biosynthesis and Engineering of Terpenoids</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Brucella: diagnosis, epidemiology, treatment</t>
-  </si>
-  <si>
     <t xml:space="preserve">Animal Ecology and Behavior Studies</t>
   </si>
   <si>
     <t xml:space="preserve">Cardiovascular Effects of Exercise</t>
   </si>
   <si>
-    <t xml:space="preserve">Plant Reproductive Biology</t>
-  </si>
-  <si>
-    <t xml:space="preserve">High Altitude and Hypoxia</t>
-  </si>
-  <si>
     <t xml:space="preserve">Molecular Biology Techniques and Applications</t>
   </si>
   <si>
-    <t xml:space="preserve">Chromium effects and bioremediation</t>
-  </si>
-  <si>
     <t xml:space="preserve">Marine Toxins and Detection Methods</t>
   </si>
   <si>
     <t xml:space="preserve">Scientific Computing and Data Management</t>
   </si>
   <si>
-    <t xml:space="preserve">Evolutionary History of Insects and Amber Fossils</t>
-  </si>
-  <si>
     <t xml:space="preserve">Spaceflight effects on biology</t>
   </si>
   <si>
@@ -848,12 +536,6 @@
     <t xml:space="preserve">Fish biology, ecology, and behavior</t>
   </si>
   <si>
-    <t xml:space="preserve">International Arbitration and Investment Law</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Satellite Communication Systems</t>
-  </si>
-  <si>
     <t xml:space="preserve">Rice Cultivation and Yield Improvement</t>
   </si>
   <si>
@@ -869,9 +551,6 @@
     <t xml:space="preserve">Isotope Analysis in Ecology</t>
   </si>
   <si>
-    <t xml:space="preserve">Peatlands and Wetlands Ecology</t>
-  </si>
-  <si>
     <t xml:space="preserve">Aquatic Invertebrate Ecology and Behavior</t>
   </si>
   <si>
@@ -884,63 +563,27 @@
     <t xml:space="preserve">Geochemistry and Geologic Mapping</t>
   </si>
   <si>
-    <t xml:space="preserve">Bacterial Identification and Susceptibility Testing</t>
-  </si>
-  <si>
     <t xml:space="preserve">Bird parasitology and diseases</t>
   </si>
   <si>
     <t xml:space="preserve">Polar Research and Ecology</t>
   </si>
   <si>
-    <t xml:space="preserve">Polysaccharides Composition and Applications</t>
-  </si>
-  <si>
-    <t xml:space="preserve">nanoparticles nucleation surface interactions</t>
-  </si>
-  <si>
     <t xml:space="preserve">Marine Ecology and Invasive Species</t>
   </si>
   <si>
-    <t xml:space="preserve">Canadian Identity and History</t>
-  </si>
-  <si>
     <t xml:space="preserve">Yersinia bacterium, plague, ectoparasites research</t>
   </si>
   <si>
     <t xml:space="preserve">Mollusks and Parasites Studies</t>
   </si>
   <si>
-    <t xml:space="preserve">Photoreceptor and optogenetics research</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mineral Processing and Grinding</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Phytochemicals and Medicinal Plants</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Fish Biology and Ecology Studies</t>
-  </si>
-  <si>
     <t xml:space="preserve">Ecology and Management of Stink Bugs</t>
   </si>
   <si>
-    <t xml:space="preserve">Geography Education and Pedagogy</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Food Chemistry and Fat Analysis</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Fern and Epiphyte Biology</t>
-  </si>
-  <si>
     <t xml:space="preserve">Study of Mite Species</t>
   </si>
   <si>
-    <t xml:space="preserve">Aeolian processes and effects</t>
-  </si>
-  <si>
     <t xml:space="preserve">Identification and Quantification in Food</t>
   </si>
   <si>
@@ -950,72 +593,33 @@
     <t xml:space="preserve">Coastal and Marine Management</t>
   </si>
   <si>
-    <t xml:space="preserve">Radiomics and Machine Learning in Medical Imaging</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Earthquake Detection and Analysis</t>
-  </si>
-  <si>
     <t xml:space="preserve">Arctic and Russian Policy Studies</t>
   </si>
   <si>
-    <t xml:space="preserve">Radio Astronomy Observations and Technology</t>
-  </si>
-  <si>
     <t xml:space="preserve">Amoebic Infections and Treatments</t>
   </si>
   <si>
     <t xml:space="preserve">History of Science and Natural History</t>
   </si>
   <si>
-    <t xml:space="preserve">Plant responses to water stress</t>
-  </si>
-  <si>
     <t xml:space="preserve">Pacific and Southeast Asian Studies</t>
   </si>
   <si>
     <t xml:space="preserve">Zoonotic diseases and public health</t>
   </si>
   <si>
-    <t xml:space="preserve">Social Acceptance of Renewable Energy</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Historical and Cultural Archaeology Studies</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sensor Technology and Measurement Systems</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Plant Taxonomy and Phylogenetics</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Photopolymerization techniques and applications</t>
-  </si>
-  <si>
     <t xml:space="preserve">vaccines and immunoinformatics approaches</t>
   </si>
   <si>
     <t xml:space="preserve">Cephalopods and Marine Biology</t>
   </si>
   <si>
-    <t xml:space="preserve">NMR spectroscopy and applications</t>
-  </si>
-  <si>
     <t xml:space="preserve">Indigenous Studies and Ecology</t>
   </si>
   <si>
-    <t xml:space="preserve">Botany and Plant Ecology Studies</t>
-  </si>
-  <si>
     <t xml:space="preserve">Maritime and Coastal Archaeology</t>
   </si>
   <si>
-    <t xml:space="preserve">Island Studies and Pacific Affairs</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Global Energy and Sustainability Research</t>
-  </si>
-  <si>
     <t xml:space="preserve">Environmental DNA in Biodiversity Studies</t>
   </si>
   <si>
@@ -1025,117 +629,36 @@
     <t xml:space="preserve">International Maritime Law Issues</t>
   </si>
   <si>
-    <t xml:space="preserve">Yeasts and Rust Fungi Studies</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Microbial Metabolism and Applications</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Smart Materials for Construction</t>
-  </si>
-  <si>
     <t xml:space="preserve">Coccidia and coccidiosis research</t>
   </si>
   <si>
-    <t xml:space="preserve">Icing and De-icing Technologies</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Water Quality Monitoring Technologies</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Economic and Financial Impacts of Cancer</t>
-  </si>
-  <si>
     <t xml:space="preserve">Space exploration and regulation</t>
   </si>
   <si>
-    <t xml:space="preserve">Aerospace Engineering and Energy Systems</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Moringa oleifera research and applications</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tree Root and Stability Studies</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Water Quality and Resources Studies</t>
-  </si>
-  <si>
     <t xml:space="preserve">Global Health Care Issues</t>
   </si>
   <si>
-    <t xml:space="preserve">Planarian Biology and Electrostimulation</t>
-  </si>
-  <si>
     <t xml:space="preserve">Ocean Acidification Effects and Responses</t>
   </si>
   <si>
     <t xml:space="preserve">Geological Formations and Processes Exploration</t>
   </si>
   <si>
-    <t xml:space="preserve">Turfgrass Adaptation and Management</t>
-  </si>
-  <si>
     <t xml:space="preserve">Biocrusts and Microbial Ecology</t>
   </si>
   <si>
-    <t xml:space="preserve">History and Developments in Astronomy</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Echinoderm biology and ecology</t>
-  </si>
-  <si>
     <t xml:space="preserve">Healthcare Systems and Challenges</t>
   </si>
   <si>
-    <t xml:space="preserve">Astronomy and Astrophysical Research</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Structural Engineering and Materials Analysis</t>
-  </si>
-  <si>
     <t xml:space="preserve">Satellite Image Processing and Photogrammetry</t>
   </si>
   <si>
-    <t xml:space="preserve">Outdoor and Experiential Education</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Seismology and Earthquake Studies</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Geology and Environmental Impact Studies</t>
-  </si>
-  <si>
     <t xml:space="preserve">Adventure Sports and Sensation Seeking</t>
   </si>
   <si>
-    <t xml:space="preserve">Geological Modeling and Analysis</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Heavy Metals in Plants</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Human Health and Disease</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mining and Gasification Technologies</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Conferences and Exhibitions Management</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Radio Wave Propagation Studies</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Advances in Oncology and Radiotherapy</t>
-  </si>
-  <si>
     <t xml:space="preserve">Scientific Research and Discoveries</t>
   </si>
   <si>
-    <t xml:space="preserve">Biotin and Related Studies</t>
-  </si>
-  <si>
     <t xml:space="preserve">Gamma-Aminobutyric Acid Metabolism in Plants</t>
   </si>
   <si>
@@ -1157,18 +680,9 @@
     <t xml:space="preserve">Spacecraft and Cryogenic Technologies</t>
   </si>
   <si>
-    <t xml:space="preserve">Environmental Changes in China</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Geological and Geophysical Studies Worldwide</t>
-  </si>
-  <si>
     <t xml:space="preserve">Artistic and Creative Research</t>
   </si>
   <si>
-    <t xml:space="preserve">Plant and Fungal Interactions Research</t>
-  </si>
-  <si>
     <t xml:space="preserve">Gothic Literature and Media Analysis</t>
   </si>
   <si>
@@ -1178,15 +692,6 @@
     <t xml:space="preserve">Diverse Scientific Research in Ukraine</t>
   </si>
   <si>
-    <t xml:space="preserve">Radio, Podcasts, and Digital Media</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Myxozoan Parasites in Aquatic Species</t>
-  </si>
-  <si>
-    <t xml:space="preserve">International Relations in Latin America</t>
-  </si>
-  <si>
     <t xml:space="preserve">Rangeland and Wildlife Management</t>
   </si>
   <si>
@@ -1199,81 +704,30 @@
     <t xml:space="preserve">Environmental Conservation and Management</t>
   </si>
   <si>
-    <t xml:space="preserve">Mineralogy and Gemology Studies</t>
-  </si>
-  <si>
     <t xml:space="preserve">Agricultural Development and Management</t>
   </si>
   <si>
     <t xml:space="preserve">Cardiovascular Health and Risk Factors</t>
   </si>
   <si>
-    <t xml:space="preserve">Environmental and biological studies</t>
-  </si>
-  <si>
     <t xml:space="preserve">Cruise Tourism Development and Management</t>
   </si>
   <si>
     <t xml:space="preserve">Chemical Analysis and Environmental Impact</t>
   </si>
   <si>
-    <t xml:space="preserve">Travel Writing and Literature</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Pasture and Agricultural Systems</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Journalism and Media Studies</t>
-  </si>
-  <si>
     <t xml:space="preserve">Marriage and Sexual Relationships</t>
   </si>
   <si>
-    <t xml:space="preserve">Historical Studies and Socio-cultural Analysis</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Computational Physics and Python Applications</t>
-  </si>
-  <si>
     <t xml:space="preserve">Tardigrade Biology and Ecology</t>
   </si>
   <si>
-    <t xml:space="preserve">Diverse Approaches in Healthcare and Education Studies</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Leech Biology and Applications</t>
-  </si>
-  <si>
     <t xml:space="preserve">Veterinary medicine and infectious diseases</t>
   </si>
   <si>
-    <t xml:space="preserve">Vietnamese History and Culture Studies</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Plant and soil sciences</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Historical Geography and Cartography</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Geophysics and Sensor Technology</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Remote Sensing and Land Use</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Diverse Interdisciplinary Research Studies</t>
-  </si>
-  <si>
     <t xml:space="preserve">Historical Art and Culture Studies</t>
   </si>
   <si>
-    <t xml:space="preserve">Genetics, Bioinformatics, and Biomedical Research</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Effects of Mining on Surface Deformations</t>
-  </si>
-  <si>
     <t xml:space="preserve">European Union Immigration and Asylum Policies</t>
   </si>
   <si>
@@ -1283,18 +737,9 @@
     <t xml:space="preserve">Conservation, Ecology, Wildlife Education</t>
   </si>
   <si>
-    <t xml:space="preserve">Geography and Environmental Studies in Latin America</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Alexander von Humboldt Studies</t>
-  </si>
-  <si>
     <t xml:space="preserve">Nutrition, Genetics, and Disease</t>
   </si>
   <si>
-    <t xml:space="preserve">Food Industry and Aquatic Biology</t>
-  </si>
-  <si>
     <t xml:space="preserve">Musicians’ Health and Performance</t>
   </si>
   <si>
@@ -1304,42 +749,18 @@
     <t xml:space="preserve">Marine and environmental studies</t>
   </si>
   <si>
-    <t xml:space="preserve">Plant and Fungal Species Descriptions</t>
-  </si>
-  <si>
     <t xml:space="preserve">Dengue and Mosquito Control Research</t>
   </si>
   <si>
     <t xml:space="preserve">Ethics, Aesthetics, and Art</t>
   </si>
   <si>
-    <t xml:space="preserve">Medical and Biological Sciences</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Agriculture, Soil, Plant Science</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Multicultural Socio-Legal Studies</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Environmental and Agricultural Sciences</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cultural and Social Studies in Latin America</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Environmental Science and Water Management</t>
-  </si>
-  <si>
     <t xml:space="preserve">Space Exploration and Technology</t>
   </si>
   <si>
     <t xml:space="preserve">Historical Gender and Feminism Studies</t>
   </si>
   <si>
-    <t xml:space="preserve">Plant-Derived Bioactive Compounds</t>
-  </si>
-  <si>
     <t xml:space="preserve">Insects and Parasite Interactions</t>
   </si>
   <si>
@@ -1355,22 +776,7 @@
     <t xml:space="preserve">Invertebrate Taxonomy and Ecology</t>
   </si>
   <si>
-    <t xml:space="preserve">Marine and Coastal Research</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Environmental Monitoring and Data Management</t>
-  </si>
-  <si>
     <t xml:space="preserve">Environmental and Cultural Studies in Latin America and Beyond</t>
-  </si>
-  <si>
-    <t xml:space="preserve">History of Science and Medicine</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Freezing and Crystallization Processes</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Diverse Historical and Scientific Studies</t>
   </si>
 </sst>
 </file>
@@ -1718,10 +1124,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>4027</v>
+        <v>1281</v>
       </c>
       <c r="B2" t="n">
-        <v>868</v>
+        <v>1075</v>
       </c>
       <c r="C2" t="n">
         <v>1</v>
@@ -1757,7 +1163,7 @@
         <v>7</v>
       </c>
       <c r="B2" t="n">
-        <v>2021</v>
+        <v>760</v>
       </c>
     </row>
     <row r="3">
@@ -1765,7 +1171,7 @@
         <v>8</v>
       </c>
       <c r="B3" t="n">
-        <v>1497</v>
+        <v>423</v>
       </c>
     </row>
     <row r="4">
@@ -1773,7 +1179,7 @@
         <v>9</v>
       </c>
       <c r="B4" t="n">
-        <v>210</v>
+        <v>26</v>
       </c>
     </row>
     <row r="5">
@@ -1781,7 +1187,7 @@
         <v>10</v>
       </c>
       <c r="B5" t="n">
-        <v>124</v>
+        <v>20</v>
       </c>
     </row>
     <row r="6">
@@ -1789,7 +1195,7 @@
         <v>11</v>
       </c>
       <c r="B6" t="n">
-        <v>62</v>
+        <v>18</v>
       </c>
     </row>
     <row r="7">
@@ -1797,7 +1203,7 @@
         <v>12</v>
       </c>
       <c r="B7" t="n">
-        <v>50</v>
+        <v>11</v>
       </c>
     </row>
     <row r="8">
@@ -1805,7 +1211,7 @@
         <v>13</v>
       </c>
       <c r="B8" t="n">
-        <v>15</v>
+        <v>8</v>
       </c>
     </row>
     <row r="9">
@@ -1813,7 +1219,7 @@
         <v>14</v>
       </c>
       <c r="B9" t="n">
-        <v>15</v>
+        <v>6</v>
       </c>
     </row>
     <row r="10">
@@ -1821,7 +1227,7 @@
         <v>15</v>
       </c>
       <c r="B10" t="n">
-        <v>13</v>
+        <v>4</v>
       </c>
     </row>
     <row r="11">
@@ -1829,7 +1235,7 @@
         <v>16</v>
       </c>
       <c r="B11" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
     </row>
     <row r="12">
@@ -1837,7 +1243,7 @@
         <v>17</v>
       </c>
       <c r="B12" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="13">
@@ -1845,7 +1251,7 @@
         <v>18</v>
       </c>
       <c r="B13" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="14">
@@ -1853,7 +1259,7 @@
         <v>19</v>
       </c>
       <c r="B14" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="15">
@@ -1861,7 +1267,7 @@
         <v>20</v>
       </c>
       <c r="B15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -1936,7 +1342,7 @@
         <v>27</v>
       </c>
       <c r="B2" t="n">
-        <v>1747</v>
+        <v>779</v>
       </c>
     </row>
     <row r="3">
@@ -1944,7 +1350,7 @@
         <v>28</v>
       </c>
       <c r="B3" t="n">
-        <v>1556</v>
+        <v>399</v>
       </c>
     </row>
     <row r="4">
@@ -1952,7 +1358,7 @@
         <v>29</v>
       </c>
       <c r="B4" t="n">
-        <v>41</v>
+        <v>17</v>
       </c>
     </row>
     <row r="5">
@@ -1960,7 +1366,7 @@
         <v>30</v>
       </c>
       <c r="B5" t="n">
-        <v>15</v>
+        <v>3</v>
       </c>
     </row>
     <row r="6">
@@ -1968,12 +1374,12 @@
         <v>31</v>
       </c>
       <c r="B6" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B7" t="n">
         <v>0</v>
@@ -2003,7 +1409,7 @@
         <v>32</v>
       </c>
       <c r="B2" t="n">
-        <v>99</v>
+        <v>5</v>
       </c>
     </row>
     <row r="3">
@@ -2011,7 +1417,7 @@
         <v>33</v>
       </c>
       <c r="B3" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="4">
@@ -2019,7 +1425,7 @@
         <v>34</v>
       </c>
       <c r="B4" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
     </row>
     <row r="5">
@@ -2027,7 +1433,7 @@
         <v>35</v>
       </c>
       <c r="B5" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="6">
@@ -2035,7 +1441,7 @@
         <v>36</v>
       </c>
       <c r="B6" t="n">
-        <v>1</v>
+        <v>17</v>
       </c>
     </row>
     <row r="7">
@@ -2043,7 +1449,7 @@
         <v>37</v>
       </c>
       <c r="B7" t="n">
-        <v>29</v>
+        <v>8</v>
       </c>
     </row>
     <row r="8">
@@ -2051,7 +1457,7 @@
         <v>38</v>
       </c>
       <c r="B8" t="n">
-        <v>1</v>
+        <v>53</v>
       </c>
     </row>
     <row r="9">
@@ -2059,7 +1465,7 @@
         <v>39</v>
       </c>
       <c r="B9" t="n">
-        <v>32</v>
+        <v>14</v>
       </c>
     </row>
     <row r="10">
@@ -2067,7 +1473,7 @@
         <v>40</v>
       </c>
       <c r="B10" t="n">
-        <v>581</v>
+        <v>25</v>
       </c>
     </row>
     <row r="11">
@@ -2075,7 +1481,7 @@
         <v>41</v>
       </c>
       <c r="B11" t="n">
-        <v>156</v>
+        <v>1</v>
       </c>
     </row>
     <row r="12">
@@ -2083,7 +1489,7 @@
         <v>42</v>
       </c>
       <c r="B12" t="n">
-        <v>124</v>
+        <v>5</v>
       </c>
     </row>
     <row r="13">
@@ -2091,7 +1497,7 @@
         <v>43</v>
       </c>
       <c r="B13" t="n">
-        <v>4</v>
+        <v>199</v>
       </c>
     </row>
     <row r="14">
@@ -2099,7 +1505,7 @@
         <v>44</v>
       </c>
       <c r="B14" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="15">
@@ -2107,7 +1513,7 @@
         <v>45</v>
       </c>
       <c r="B15" t="n">
-        <v>61</v>
+        <v>7</v>
       </c>
     </row>
     <row r="16">
@@ -2115,7 +1521,7 @@
         <v>46</v>
       </c>
       <c r="B16" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="17">
@@ -2123,7 +1529,7 @@
         <v>47</v>
       </c>
       <c r="B17" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="18">
@@ -2131,7 +1537,7 @@
         <v>48</v>
       </c>
       <c r="B18" t="n">
-        <v>223</v>
+        <v>1</v>
       </c>
     </row>
     <row r="19">
@@ -2139,7 +1545,7 @@
         <v>49</v>
       </c>
       <c r="B19" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="20">
@@ -2155,7 +1561,7 @@
         <v>51</v>
       </c>
       <c r="B21" t="n">
-        <v>87</v>
+        <v>1</v>
       </c>
     </row>
     <row r="22">
@@ -2163,7 +1569,7 @@
         <v>52</v>
       </c>
       <c r="B22" t="n">
-        <v>32</v>
+        <v>1</v>
       </c>
     </row>
     <row r="23">
@@ -2171,7 +1577,7 @@
         <v>53</v>
       </c>
       <c r="B23" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="24">
@@ -2179,7 +1585,7 @@
         <v>54</v>
       </c>
       <c r="B24" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="25">
@@ -2187,7 +1593,7 @@
         <v>55</v>
       </c>
       <c r="B25" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="26">
@@ -2203,7 +1609,7 @@
         <v>57</v>
       </c>
       <c r="B27" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="28">
@@ -2211,7 +1617,7 @@
         <v>58</v>
       </c>
       <c r="B28" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
     </row>
     <row r="29">
@@ -2227,7 +1633,7 @@
         <v>60</v>
       </c>
       <c r="B30" t="n">
-        <v>3</v>
+        <v>107</v>
       </c>
     </row>
     <row r="31">
@@ -2235,7 +1641,7 @@
         <v>61</v>
       </c>
       <c r="B31" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="32">
@@ -2243,7 +1649,7 @@
         <v>62</v>
       </c>
       <c r="B32" t="n">
-        <v>19</v>
+        <v>1</v>
       </c>
     </row>
     <row r="33">
@@ -2251,7 +1657,7 @@
         <v>63</v>
       </c>
       <c r="B33" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="34">
@@ -2259,7 +1665,7 @@
         <v>64</v>
       </c>
       <c r="B34" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="35">
@@ -2267,7 +1673,7 @@
         <v>65</v>
       </c>
       <c r="B35" t="n">
-        <v>21</v>
+        <v>3</v>
       </c>
     </row>
     <row r="36">
@@ -2275,7 +1681,7 @@
         <v>66</v>
       </c>
       <c r="B36" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
     </row>
     <row r="37">
@@ -2283,7 +1689,7 @@
         <v>67</v>
       </c>
       <c r="B37" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
     </row>
     <row r="38">
@@ -2299,7 +1705,7 @@
         <v>69</v>
       </c>
       <c r="B39" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="40">
@@ -2307,7 +1713,7 @@
         <v>70</v>
       </c>
       <c r="B40" t="n">
-        <v>27</v>
+        <v>34</v>
       </c>
     </row>
     <row r="41">
@@ -2315,7 +1721,7 @@
         <v>71</v>
       </c>
       <c r="B41" t="n">
-        <v>1</v>
+        <v>19</v>
       </c>
     </row>
     <row r="42">
@@ -2331,7 +1737,7 @@
         <v>73</v>
       </c>
       <c r="B43" t="n">
-        <v>166</v>
+        <v>6</v>
       </c>
     </row>
     <row r="44">
@@ -2347,7 +1753,7 @@
         <v>75</v>
       </c>
       <c r="B45" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="46">
@@ -2363,7 +1769,7 @@
         <v>77</v>
       </c>
       <c r="B47" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="48">
@@ -2371,7 +1777,7 @@
         <v>78</v>
       </c>
       <c r="B48" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
     </row>
     <row r="49">
@@ -2379,7 +1785,7 @@
         <v>79</v>
       </c>
       <c r="B49" t="n">
-        <v>11</v>
+        <v>4</v>
       </c>
     </row>
     <row r="50">
@@ -2387,7 +1793,7 @@
         <v>80</v>
       </c>
       <c r="B50" t="n">
-        <v>34</v>
+        <v>1</v>
       </c>
     </row>
     <row r="51">
@@ -2403,7 +1809,7 @@
         <v>82</v>
       </c>
       <c r="B52" t="n">
-        <v>11</v>
+        <v>2</v>
       </c>
     </row>
     <row r="53">
@@ -2411,7 +1817,7 @@
         <v>83</v>
       </c>
       <c r="B53" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="54">
@@ -2427,7 +1833,7 @@
         <v>85</v>
       </c>
       <c r="B55" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="56">
@@ -2435,7 +1841,7 @@
         <v>86</v>
       </c>
       <c r="B56" t="n">
-        <v>60</v>
+        <v>1</v>
       </c>
     </row>
     <row r="57">
@@ -2443,7 +1849,7 @@
         <v>87</v>
       </c>
       <c r="B57" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
     </row>
     <row r="58">
@@ -2451,7 +1857,7 @@
         <v>88</v>
       </c>
       <c r="B58" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
     </row>
     <row r="59">
@@ -2459,7 +1865,7 @@
         <v>89</v>
       </c>
       <c r="B59" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="60">
@@ -2475,7 +1881,7 @@
         <v>91</v>
       </c>
       <c r="B61" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="62">
@@ -2483,7 +1889,7 @@
         <v>92</v>
       </c>
       <c r="B62" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="63">
@@ -2491,7 +1897,7 @@
         <v>93</v>
       </c>
       <c r="B63" t="n">
-        <v>51</v>
+        <v>35</v>
       </c>
     </row>
     <row r="64">
@@ -2499,7 +1905,7 @@
         <v>94</v>
       </c>
       <c r="B64" t="n">
-        <v>28</v>
+        <v>38</v>
       </c>
     </row>
     <row r="65">
@@ -2507,7 +1913,7 @@
         <v>95</v>
       </c>
       <c r="B65" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="66">
@@ -2515,7 +1921,7 @@
         <v>96</v>
       </c>
       <c r="B66" t="n">
-        <v>14</v>
+        <v>131</v>
       </c>
     </row>
     <row r="67">
@@ -2523,7 +1929,7 @@
         <v>97</v>
       </c>
       <c r="B67" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="68">
@@ -2531,7 +1937,7 @@
         <v>98</v>
       </c>
       <c r="B68" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="69">
@@ -2539,7 +1945,7 @@
         <v>99</v>
       </c>
       <c r="B69" t="n">
-        <v>12</v>
+        <v>2</v>
       </c>
     </row>
     <row r="70">
@@ -2547,7 +1953,7 @@
         <v>100</v>
       </c>
       <c r="B70" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="71">
@@ -2555,7 +1961,7 @@
         <v>101</v>
       </c>
       <c r="B71" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="72">
@@ -2563,7 +1969,7 @@
         <v>102</v>
       </c>
       <c r="B72" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
     </row>
     <row r="73">
@@ -2571,7 +1977,7 @@
         <v>103</v>
       </c>
       <c r="B73" t="n">
-        <v>1</v>
+        <v>29</v>
       </c>
     </row>
     <row r="74">
@@ -2579,7 +1985,7 @@
         <v>104</v>
       </c>
       <c r="B74" t="n">
-        <v>14</v>
+        <v>1</v>
       </c>
     </row>
     <row r="75">
@@ -2587,7 +1993,7 @@
         <v>105</v>
       </c>
       <c r="B75" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="76">
@@ -2595,7 +2001,7 @@
         <v>106</v>
       </c>
       <c r="B76" t="n">
-        <v>22</v>
+        <v>5</v>
       </c>
     </row>
     <row r="77">
@@ -2603,7 +2009,7 @@
         <v>107</v>
       </c>
       <c r="B77" t="n">
-        <v>1</v>
+        <v>15</v>
       </c>
     </row>
     <row r="78">
@@ -2611,7 +2017,7 @@
         <v>108</v>
       </c>
       <c r="B78" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="79">
@@ -2627,7 +2033,7 @@
         <v>110</v>
       </c>
       <c r="B80" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="81">
@@ -2635,7 +2041,7 @@
         <v>111</v>
       </c>
       <c r="B81" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
     </row>
     <row r="82">
@@ -2643,7 +2049,7 @@
         <v>112</v>
       </c>
       <c r="B82" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="83">
@@ -2651,7 +2057,7 @@
         <v>113</v>
       </c>
       <c r="B83" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="84">
@@ -2659,7 +2065,7 @@
         <v>114</v>
       </c>
       <c r="B84" t="n">
-        <v>22</v>
+        <v>40</v>
       </c>
     </row>
     <row r="85">
@@ -2667,7 +2073,7 @@
         <v>115</v>
       </c>
       <c r="B85" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
     </row>
     <row r="86">
@@ -2675,7 +2081,7 @@
         <v>116</v>
       </c>
       <c r="B86" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="87">
@@ -2683,7 +2089,7 @@
         <v>117</v>
       </c>
       <c r="B87" t="n">
-        <v>12</v>
+        <v>3</v>
       </c>
     </row>
     <row r="88">
@@ -2691,7 +2097,7 @@
         <v>118</v>
       </c>
       <c r="B88" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
     </row>
     <row r="89">
@@ -2699,7 +2105,7 @@
         <v>119</v>
       </c>
       <c r="B89" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="90">
@@ -2707,7 +2113,7 @@
         <v>120</v>
       </c>
       <c r="B90" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="91">
@@ -2715,7 +2121,7 @@
         <v>121</v>
       </c>
       <c r="B91" t="n">
-        <v>99</v>
+        <v>12</v>
       </c>
     </row>
     <row r="92">
@@ -2731,7 +2137,7 @@
         <v>123</v>
       </c>
       <c r="B93" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="94">
@@ -2739,7 +2145,7 @@
         <v>124</v>
       </c>
       <c r="B94" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
     </row>
     <row r="95">
@@ -2755,7 +2161,7 @@
         <v>126</v>
       </c>
       <c r="B96" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="97">
@@ -2771,7 +2177,7 @@
         <v>128</v>
       </c>
       <c r="B98" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="99">
@@ -2779,7 +2185,7 @@
         <v>129</v>
       </c>
       <c r="B99" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="100">
@@ -2787,7 +2193,7 @@
         <v>130</v>
       </c>
       <c r="B100" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="101">
@@ -2803,7 +2209,7 @@
         <v>132</v>
       </c>
       <c r="B102" t="n">
-        <v>153</v>
+        <v>3</v>
       </c>
     </row>
     <row r="103">
@@ -2811,7 +2217,7 @@
         <v>133</v>
       </c>
       <c r="B103" t="n">
-        <v>827</v>
+        <v>2</v>
       </c>
     </row>
     <row r="104">
@@ -2819,7 +2225,7 @@
         <v>134</v>
       </c>
       <c r="B104" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="105">
@@ -2827,7 +2233,7 @@
         <v>135</v>
       </c>
       <c r="B105" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
     </row>
     <row r="106">
@@ -2835,7 +2241,7 @@
         <v>136</v>
       </c>
       <c r="B106" t="n">
-        <v>204</v>
+        <v>14</v>
       </c>
     </row>
     <row r="107">
@@ -2843,7 +2249,7 @@
         <v>137</v>
       </c>
       <c r="B107" t="n">
-        <v>1</v>
+        <v>11</v>
       </c>
     </row>
     <row r="108">
@@ -2851,7 +2257,7 @@
         <v>138</v>
       </c>
       <c r="B108" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="109">
@@ -2867,7 +2273,7 @@
         <v>140</v>
       </c>
       <c r="B110" t="n">
-        <v>2</v>
+        <v>36</v>
       </c>
     </row>
     <row r="111">
@@ -2875,7 +2281,7 @@
         <v>141</v>
       </c>
       <c r="B111" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="112">
@@ -2883,7 +2289,7 @@
         <v>142</v>
       </c>
       <c r="B112" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="113">
@@ -2891,7 +2297,7 @@
         <v>143</v>
       </c>
       <c r="B113" t="n">
-        <v>21</v>
+        <v>5</v>
       </c>
     </row>
     <row r="114">
@@ -2907,7 +2313,7 @@
         <v>145</v>
       </c>
       <c r="B115" t="n">
-        <v>13</v>
+        <v>3</v>
       </c>
     </row>
     <row r="116">
@@ -2915,7 +2321,7 @@
         <v>146</v>
       </c>
       <c r="B116" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="117">
@@ -2931,7 +2337,7 @@
         <v>148</v>
       </c>
       <c r="B118" t="n">
-        <v>231</v>
+        <v>5</v>
       </c>
     </row>
     <row r="119">
@@ -2939,7 +2345,7 @@
         <v>149</v>
       </c>
       <c r="B119" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="120">
@@ -2947,7 +2353,7 @@
         <v>150</v>
       </c>
       <c r="B120" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="121">
@@ -2955,7 +2361,7 @@
         <v>151</v>
       </c>
       <c r="B121" t="n">
-        <v>2</v>
+        <v>11</v>
       </c>
     </row>
     <row r="122">
@@ -2979,7 +2385,7 @@
         <v>154</v>
       </c>
       <c r="B124" t="n">
-        <v>12</v>
+        <v>2</v>
       </c>
     </row>
     <row r="125">
@@ -2987,7 +2393,7 @@
         <v>155</v>
       </c>
       <c r="B125" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
     </row>
     <row r="126">
@@ -2995,7 +2401,7 @@
         <v>156</v>
       </c>
       <c r="B126" t="n">
-        <v>26</v>
+        <v>1</v>
       </c>
     </row>
     <row r="127">
@@ -3003,7 +2409,7 @@
         <v>157</v>
       </c>
       <c r="B127" t="n">
-        <v>18</v>
+        <v>2</v>
       </c>
     </row>
     <row r="128">
@@ -3011,7 +2417,7 @@
         <v>158</v>
       </c>
       <c r="B128" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="129">
@@ -3027,7 +2433,7 @@
         <v>160</v>
       </c>
       <c r="B130" t="n">
-        <v>4</v>
+        <v>22</v>
       </c>
     </row>
     <row r="131">
@@ -3035,7 +2441,7 @@
         <v>161</v>
       </c>
       <c r="B131" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="132">
@@ -3059,7 +2465,7 @@
         <v>164</v>
       </c>
       <c r="B134" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
     </row>
     <row r="135">
@@ -3067,7 +2473,7 @@
         <v>165</v>
       </c>
       <c r="B135" t="n">
-        <v>73</v>
+        <v>4</v>
       </c>
     </row>
     <row r="136">
@@ -3091,7 +2497,7 @@
         <v>168</v>
       </c>
       <c r="B138" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
     </row>
     <row r="139">
@@ -3099,7 +2505,7 @@
         <v>169</v>
       </c>
       <c r="B139" t="n">
-        <v>30</v>
+        <v>2</v>
       </c>
     </row>
     <row r="140">
@@ -3107,7 +2513,7 @@
         <v>170</v>
       </c>
       <c r="B140" t="n">
-        <v>53</v>
+        <v>4</v>
       </c>
     </row>
     <row r="141">
@@ -3123,7 +2529,7 @@
         <v>172</v>
       </c>
       <c r="B142" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="143">
@@ -3131,7 +2537,7 @@
         <v>173</v>
       </c>
       <c r="B143" t="n">
-        <v>80</v>
+        <v>1</v>
       </c>
     </row>
     <row r="144">
@@ -3139,7 +2545,7 @@
         <v>174</v>
       </c>
       <c r="B144" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="145">
@@ -3147,7 +2553,7 @@
         <v>175</v>
       </c>
       <c r="B145" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
     </row>
     <row r="146">
@@ -3155,7 +2561,7 @@
         <v>176</v>
       </c>
       <c r="B146" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="147">
@@ -3163,7 +2569,7 @@
         <v>177</v>
       </c>
       <c r="B147" t="n">
-        <v>1</v>
+        <v>37</v>
       </c>
     </row>
     <row r="148">
@@ -3171,7 +2577,7 @@
         <v>178</v>
       </c>
       <c r="B148" t="n">
-        <v>11</v>
+        <v>2</v>
       </c>
     </row>
     <row r="149">
@@ -3179,7 +2585,7 @@
         <v>179</v>
       </c>
       <c r="B149" t="n">
-        <v>30</v>
+        <v>1</v>
       </c>
     </row>
     <row r="150">
@@ -3195,7 +2601,7 @@
         <v>181</v>
       </c>
       <c r="B151" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="152">
@@ -3203,7 +2609,7 @@
         <v>182</v>
       </c>
       <c r="B152" t="n">
-        <v>4</v>
+        <v>12</v>
       </c>
     </row>
     <row r="153">
@@ -3211,7 +2617,7 @@
         <v>183</v>
       </c>
       <c r="B153" t="n">
-        <v>68</v>
+        <v>129</v>
       </c>
     </row>
     <row r="154">
@@ -3227,7 +2633,7 @@
         <v>185</v>
       </c>
       <c r="B155" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="156">
@@ -3251,7 +2657,7 @@
         <v>188</v>
       </c>
       <c r="B158" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="159">
@@ -3259,7 +2665,7 @@
         <v>189</v>
       </c>
       <c r="B159" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="160">
@@ -3267,7 +2673,7 @@
         <v>190</v>
       </c>
       <c r="B160" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="161">
@@ -3275,7 +2681,7 @@
         <v>191</v>
       </c>
       <c r="B161" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
     </row>
     <row r="162">
@@ -3283,7 +2689,7 @@
         <v>192</v>
       </c>
       <c r="B162" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="163">
@@ -3299,7 +2705,7 @@
         <v>194</v>
       </c>
       <c r="B164" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="165">
@@ -3307,7 +2713,7 @@
         <v>195</v>
       </c>
       <c r="B165" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="166">
@@ -3315,7 +2721,7 @@
         <v>196</v>
       </c>
       <c r="B166" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="167">
@@ -3323,7 +2729,7 @@
         <v>197</v>
       </c>
       <c r="B167" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="168">
@@ -3331,7 +2737,7 @@
         <v>198</v>
       </c>
       <c r="B168" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="169">
@@ -3339,7 +2745,7 @@
         <v>199</v>
       </c>
       <c r="B169" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="170">
@@ -3347,7 +2753,7 @@
         <v>200</v>
       </c>
       <c r="B170" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="171">
@@ -3355,7 +2761,7 @@
         <v>201</v>
       </c>
       <c r="B171" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="172">
@@ -3379,7 +2785,7 @@
         <v>204</v>
       </c>
       <c r="B174" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="175">
@@ -3395,7 +2801,7 @@
         <v>206</v>
       </c>
       <c r="B176" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="177">
@@ -3403,7 +2809,7 @@
         <v>207</v>
       </c>
       <c r="B177" t="n">
-        <v>39</v>
+        <v>8</v>
       </c>
     </row>
     <row r="178">
@@ -3411,7 +2817,7 @@
         <v>208</v>
       </c>
       <c r="B178" t="n">
-        <v>168</v>
+        <v>1</v>
       </c>
     </row>
     <row r="179">
@@ -3419,7 +2825,7 @@
         <v>209</v>
       </c>
       <c r="B179" t="n">
-        <v>17</v>
+        <v>2</v>
       </c>
     </row>
     <row r="180">
@@ -3435,7 +2841,7 @@
         <v>211</v>
       </c>
       <c r="B181" t="n">
-        <v>34</v>
+        <v>65</v>
       </c>
     </row>
     <row r="182">
@@ -3443,7 +2849,7 @@
         <v>212</v>
       </c>
       <c r="B182" t="n">
-        <v>28</v>
+        <v>3</v>
       </c>
     </row>
     <row r="183">
@@ -3459,7 +2865,7 @@
         <v>214</v>
       </c>
       <c r="B184" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="185">
@@ -3467,7 +2873,7 @@
         <v>215</v>
       </c>
       <c r="B185" t="n">
-        <v>53</v>
+        <v>3</v>
       </c>
     </row>
     <row r="186">
@@ -3475,7 +2881,7 @@
         <v>216</v>
       </c>
       <c r="B186" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="187">
@@ -3483,7 +2889,7 @@
         <v>217</v>
       </c>
       <c r="B187" t="n">
-        <v>262</v>
+        <v>1</v>
       </c>
     </row>
     <row r="188">
@@ -3499,7 +2905,7 @@
         <v>219</v>
       </c>
       <c r="B189" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="190">
@@ -3507,7 +2913,7 @@
         <v>220</v>
       </c>
       <c r="B190" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="191">
@@ -3515,7 +2921,7 @@
         <v>221</v>
       </c>
       <c r="B191" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
     </row>
     <row r="192">
@@ -3531,7 +2937,7 @@
         <v>223</v>
       </c>
       <c r="B193" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="194">
@@ -3539,7 +2945,7 @@
         <v>224</v>
       </c>
       <c r="B194" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="195">
@@ -3547,7 +2953,7 @@
         <v>225</v>
       </c>
       <c r="B195" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="196">
@@ -3555,7 +2961,7 @@
         <v>226</v>
       </c>
       <c r="B196" t="n">
-        <v>58</v>
+        <v>2</v>
       </c>
     </row>
     <row r="197">
@@ -3563,7 +2969,7 @@
         <v>227</v>
       </c>
       <c r="B197" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="198">
@@ -3571,7 +2977,7 @@
         <v>228</v>
       </c>
       <c r="B198" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="199">
@@ -3579,7 +2985,7 @@
         <v>229</v>
       </c>
       <c r="B199" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="200">
@@ -3587,7 +2993,7 @@
         <v>230</v>
       </c>
       <c r="B200" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="201">
@@ -3595,7 +3001,7 @@
         <v>231</v>
       </c>
       <c r="B201" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="202">
@@ -3611,7 +3017,7 @@
         <v>233</v>
       </c>
       <c r="B203" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="204">
@@ -3619,7 +3025,7 @@
         <v>234</v>
       </c>
       <c r="B204" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="205">
@@ -3627,7 +3033,7 @@
         <v>235</v>
       </c>
       <c r="B205" t="n">
-        <v>107</v>
+        <v>1</v>
       </c>
     </row>
     <row r="206">
@@ -3635,7 +3041,7 @@
         <v>236</v>
       </c>
       <c r="B206" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
     </row>
     <row r="207">
@@ -3651,7 +3057,7 @@
         <v>238</v>
       </c>
       <c r="B208" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="209">
@@ -3659,7 +3065,7 @@
         <v>239</v>
       </c>
       <c r="B209" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="210">
@@ -3667,7 +3073,7 @@
         <v>240</v>
       </c>
       <c r="B210" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="211">
@@ -3683,7 +3089,7 @@
         <v>242</v>
       </c>
       <c r="B212" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="213">
@@ -3691,7 +3097,7 @@
         <v>243</v>
       </c>
       <c r="B213" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="214">
@@ -3699,7 +3105,7 @@
         <v>244</v>
       </c>
       <c r="B214" t="n">
-        <v>12</v>
+        <v>2</v>
       </c>
     </row>
     <row r="215">
@@ -3715,7 +3121,7 @@
         <v>246</v>
       </c>
       <c r="B216" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="217">
@@ -3723,7 +3129,7 @@
         <v>247</v>
       </c>
       <c r="B217" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="218">
@@ -3731,7 +3137,7 @@
         <v>248</v>
       </c>
       <c r="B218" t="n">
-        <v>11</v>
+        <v>1</v>
       </c>
     </row>
     <row r="219">
@@ -3755,7 +3161,7 @@
         <v>251</v>
       </c>
       <c r="B221" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
     </row>
     <row r="222">
@@ -3763,7 +3169,7 @@
         <v>252</v>
       </c>
       <c r="B222" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="223">
@@ -3771,1591 +3177,7 @@
         <v>253</v>
       </c>
       <c r="B223" t="n">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="224">
-      <c r="A224" t="s">
-        <v>254</v>
-      </c>
-      <c r="B224" t="n">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="225">
-      <c r="A225" t="s">
-        <v>255</v>
-      </c>
-      <c r="B225" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="226">
-      <c r="A226" t="s">
-        <v>256</v>
-      </c>
-      <c r="B226" t="n">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="227">
-      <c r="A227" t="s">
-        <v>257</v>
-      </c>
-      <c r="B227" t="n">
-        <v>173</v>
-      </c>
-    </row>
-    <row r="228">
-      <c r="A228" t="s">
-        <v>258</v>
-      </c>
-      <c r="B228" t="n">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="229">
-      <c r="A229" t="s">
-        <v>259</v>
-      </c>
-      <c r="B229" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="230">
-      <c r="A230" t="s">
-        <v>260</v>
-      </c>
-      <c r="B230" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="231">
-      <c r="A231" t="s">
-        <v>261</v>
-      </c>
-      <c r="B231" t="n">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="232">
-      <c r="A232" t="s">
-        <v>262</v>
-      </c>
-      <c r="B232" t="n">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="233">
-      <c r="A233" t="s">
-        <v>263</v>
-      </c>
-      <c r="B233" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="234">
-      <c r="A234" t="s">
-        <v>264</v>
-      </c>
-      <c r="B234" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="235">
-      <c r="A235" t="s">
-        <v>265</v>
-      </c>
-      <c r="B235" t="n">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="236">
-      <c r="A236" t="s">
-        <v>266</v>
-      </c>
-      <c r="B236" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="237">
-      <c r="A237" t="s">
-        <v>267</v>
-      </c>
-      <c r="B237" t="n">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="238">
-      <c r="A238" t="s">
-        <v>268</v>
-      </c>
-      <c r="B238" t="n">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="239">
-      <c r="A239" t="s">
-        <v>269</v>
-      </c>
-      <c r="B239" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="240">
-      <c r="A240" t="s">
-        <v>270</v>
-      </c>
-      <c r="B240" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="241">
-      <c r="A241" t="s">
-        <v>271</v>
-      </c>
-      <c r="B241" t="n">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="242">
-      <c r="A242" t="s">
-        <v>272</v>
-      </c>
-      <c r="B242" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="243">
-      <c r="A243" t="s">
-        <v>273</v>
-      </c>
-      <c r="B243" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="244">
-      <c r="A244" t="s">
-        <v>274</v>
-      </c>
-      <c r="B244" t="n">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="245">
-      <c r="A245" t="s">
-        <v>275</v>
-      </c>
-      <c r="B245" t="n">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="246">
-      <c r="A246" t="s">
-        <v>276</v>
-      </c>
-      <c r="B246" t="n">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="247">
-      <c r="A247" t="s">
-        <v>277</v>
-      </c>
-      <c r="B247" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="248">
-      <c r="A248" t="s">
-        <v>278</v>
-      </c>
-      <c r="B248" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="249">
-      <c r="A249" t="s">
-        <v>279</v>
-      </c>
-      <c r="B249" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="250">
-      <c r="A250" t="s">
-        <v>280</v>
-      </c>
-      <c r="B250" t="n">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="251">
-      <c r="A251" t="s">
-        <v>281</v>
-      </c>
-      <c r="B251" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="252">
-      <c r="A252" t="s">
-        <v>282</v>
-      </c>
-      <c r="B252" t="n">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="253">
-      <c r="A253" t="s">
-        <v>283</v>
-      </c>
-      <c r="B253" t="n">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="254">
-      <c r="A254" t="s">
-        <v>284</v>
-      </c>
-      <c r="B254" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="255">
-      <c r="A255" t="s">
-        <v>285</v>
-      </c>
-      <c r="B255" t="n">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="256">
-      <c r="A256" t="s">
-        <v>286</v>
-      </c>
-      <c r="B256" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="257">
-      <c r="A257" t="s">
-        <v>287</v>
-      </c>
-      <c r="B257" t="n">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="258">
-      <c r="A258" t="s">
-        <v>288</v>
-      </c>
-      <c r="B258" t="n">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="259">
-      <c r="A259" t="s">
-        <v>289</v>
-      </c>
-      <c r="B259" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="260">
-      <c r="A260" t="s">
-        <v>290</v>
-      </c>
-      <c r="B260" t="n">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="261">
-      <c r="A261" t="s">
-        <v>291</v>
-      </c>
-      <c r="B261" t="n">
-        <v>887</v>
-      </c>
-    </row>
-    <row r="262">
-      <c r="A262" t="s">
-        <v>292</v>
-      </c>
-      <c r="B262" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="263">
-      <c r="A263" t="s">
-        <v>293</v>
-      </c>
-      <c r="B263" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="264">
-      <c r="A264" t="s">
-        <v>294</v>
-      </c>
-      <c r="B264" t="n">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="265">
-      <c r="A265" t="s">
-        <v>295</v>
-      </c>
-      <c r="B265" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="266">
-      <c r="A266" t="s">
-        <v>296</v>
-      </c>
-      <c r="B266" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="267">
-      <c r="A267" t="s">
-        <v>297</v>
-      </c>
-      <c r="B267" t="n">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="268">
-      <c r="A268" t="s">
-        <v>298</v>
-      </c>
-      <c r="B268" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="269">
-      <c r="A269" t="s">
-        <v>299</v>
-      </c>
-      <c r="B269" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="270">
-      <c r="A270" t="s">
-        <v>300</v>
-      </c>
-      <c r="B270" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="271">
-      <c r="A271" t="s">
-        <v>301</v>
-      </c>
-      <c r="B271" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="272">
-      <c r="A272" t="s">
-        <v>302</v>
-      </c>
-      <c r="B272" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="273">
-      <c r="A273" t="s">
-        <v>303</v>
-      </c>
-      <c r="B273" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="274">
-      <c r="A274" t="s">
-        <v>304</v>
-      </c>
-      <c r="B274" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="275">
-      <c r="A275" t="s">
-        <v>305</v>
-      </c>
-      <c r="B275" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="276">
-      <c r="A276" t="s">
-        <v>306</v>
-      </c>
-      <c r="B276" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="277">
-      <c r="A277" t="s">
-        <v>307</v>
-      </c>
-      <c r="B277" t="n">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="278">
-      <c r="A278" t="s">
-        <v>308</v>
-      </c>
-      <c r="B278" t="n">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="279">
-      <c r="A279" t="s">
-        <v>309</v>
-      </c>
-      <c r="B279" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="280">
-      <c r="A280" t="s">
-        <v>310</v>
-      </c>
-      <c r="B280" t="n">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="281">
-      <c r="A281" t="s">
-        <v>311</v>
-      </c>
-      <c r="B281" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="282">
-      <c r="A282" t="s">
-        <v>312</v>
-      </c>
-      <c r="B282" t="n">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="283">
-      <c r="A283" t="s">
-        <v>313</v>
-      </c>
-      <c r="B283" t="n">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="284">
-      <c r="A284" t="s">
-        <v>314</v>
-      </c>
-      <c r="B284" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="285">
-      <c r="A285" t="s">
-        <v>315</v>
-      </c>
-      <c r="B285" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="286">
-      <c r="A286" t="s">
-        <v>316</v>
-      </c>
-      <c r="B286" t="n">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="287">
-      <c r="A287" t="s">
-        <v>317</v>
-      </c>
-      <c r="B287" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="288">
-      <c r="A288" t="s">
-        <v>318</v>
-      </c>
-      <c r="B288" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="289">
-      <c r="A289" t="s">
-        <v>319</v>
-      </c>
-      <c r="B289" t="n">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="290">
-      <c r="A290" t="s">
-        <v>320</v>
-      </c>
-      <c r="B290" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="291">
-      <c r="A291" t="s">
-        <v>321</v>
-      </c>
-      <c r="B291" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="292">
-      <c r="A292" t="s">
-        <v>322</v>
-      </c>
-      <c r="B292" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="293">
-      <c r="A293" t="s">
-        <v>323</v>
-      </c>
-      <c r="B293" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="294">
-      <c r="A294" t="s">
-        <v>324</v>
-      </c>
-      <c r="B294" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="295">
-      <c r="A295" t="s">
-        <v>325</v>
-      </c>
-      <c r="B295" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="296">
-      <c r="A296" t="s">
-        <v>326</v>
-      </c>
-      <c r="B296" t="n">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="297">
-      <c r="A297" t="s">
-        <v>327</v>
-      </c>
-      <c r="B297" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="298">
-      <c r="A298" t="s">
-        <v>328</v>
-      </c>
-      <c r="B298" t="n">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="299">
-      <c r="A299" t="s">
-        <v>329</v>
-      </c>
-      <c r="B299" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="300">
-      <c r="A300" t="s">
-        <v>330</v>
-      </c>
-      <c r="B300" t="n">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="301">
-      <c r="A301" t="s">
-        <v>331</v>
-      </c>
-      <c r="B301" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="302">
-      <c r="A302" t="s">
-        <v>332</v>
-      </c>
-      <c r="B302" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="303">
-      <c r="A303" t="s">
-        <v>333</v>
-      </c>
-      <c r="B303" t="n">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="304">
-      <c r="A304" t="s">
-        <v>334</v>
-      </c>
-      <c r="B304" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="305">
-      <c r="A305" t="s">
-        <v>335</v>
-      </c>
-      <c r="B305" t="n">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="306">
-      <c r="A306" t="s">
-        <v>336</v>
-      </c>
-      <c r="B306" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="307">
-      <c r="A307" t="s">
-        <v>337</v>
-      </c>
-      <c r="B307" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="308">
-      <c r="A308" t="s">
-        <v>338</v>
-      </c>
-      <c r="B308" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="309">
-      <c r="A309" t="s">
-        <v>339</v>
-      </c>
-      <c r="B309" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="310">
-      <c r="A310" t="s">
-        <v>340</v>
-      </c>
-      <c r="B310" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="311">
-      <c r="A311" t="s">
-        <v>341</v>
-      </c>
-      <c r="B311" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="312">
-      <c r="A312" t="s">
-        <v>342</v>
-      </c>
-      <c r="B312" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="313">
-      <c r="A313" t="s">
-        <v>343</v>
-      </c>
-      <c r="B313" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="314">
-      <c r="A314" t="s">
-        <v>344</v>
-      </c>
-      <c r="B314" t="n">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="315">
-      <c r="A315" t="s">
-        <v>345</v>
-      </c>
-      <c r="B315" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="316">
-      <c r="A316" t="s">
-        <v>346</v>
-      </c>
-      <c r="B316" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="317">
-      <c r="A317" t="s">
-        <v>347</v>
-      </c>
-      <c r="B317" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="318">
-      <c r="A318" t="s">
-        <v>348</v>
-      </c>
-      <c r="B318" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="319">
-      <c r="A319" t="s">
-        <v>349</v>
-      </c>
-      <c r="B319" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="320">
-      <c r="A320" t="s">
-        <v>350</v>
-      </c>
-      <c r="B320" t="n">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="321">
-      <c r="A321" t="s">
-        <v>351</v>
-      </c>
-      <c r="B321" t="n">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="322">
-      <c r="A322" t="s">
-        <v>352</v>
-      </c>
-      <c r="B322" t="n">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="323">
-      <c r="A323" t="s">
-        <v>353</v>
-      </c>
-      <c r="B323" t="n">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="324">
-      <c r="A324" t="s">
-        <v>354</v>
-      </c>
-      <c r="B324" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="325">
-      <c r="A325" t="s">
-        <v>355</v>
-      </c>
-      <c r="B325" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="326">
-      <c r="A326" t="s">
-        <v>356</v>
-      </c>
-      <c r="B326" t="n">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="327">
-      <c r="A327" t="s">
-        <v>357</v>
-      </c>
-      <c r="B327" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="328">
-      <c r="A328" t="s">
-        <v>358</v>
-      </c>
-      <c r="B328" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="329">
-      <c r="A329" t="s">
-        <v>359</v>
-      </c>
-      <c r="B329" t="n">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="330">
-      <c r="A330" t="s">
-        <v>360</v>
-      </c>
-      <c r="B330" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="331">
-      <c r="A331" t="s">
-        <v>361</v>
-      </c>
-      <c r="B331" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="332">
-      <c r="A332" t="s">
-        <v>362</v>
-      </c>
-      <c r="B332" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="333">
-      <c r="A333" t="s">
-        <v>363</v>
-      </c>
-      <c r="B333" t="n">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="334">
-      <c r="A334" t="s">
-        <v>364</v>
-      </c>
-      <c r="B334" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="335">
-      <c r="A335" t="s">
-        <v>365</v>
-      </c>
-      <c r="B335" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="336">
-      <c r="A336" t="s">
-        <v>366</v>
-      </c>
-      <c r="B336" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="337">
-      <c r="A337" t="s">
-        <v>367</v>
-      </c>
-      <c r="B337" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="338">
-      <c r="A338" t="s">
-        <v>368</v>
-      </c>
-      <c r="B338" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="339">
-      <c r="A339" t="s">
-        <v>369</v>
-      </c>
-      <c r="B339" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="340">
-      <c r="A340" t="s">
-        <v>370</v>
-      </c>
-      <c r="B340" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="341">
-      <c r="A341" t="s">
-        <v>371</v>
-      </c>
-      <c r="B341" t="n">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="342">
-      <c r="A342" t="s">
-        <v>372</v>
-      </c>
-      <c r="B342" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="343">
-      <c r="A343" t="s">
-        <v>373</v>
-      </c>
-      <c r="B343" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="344">
-      <c r="A344" t="s">
-        <v>374</v>
-      </c>
-      <c r="B344" t="n">
-        <v>253</v>
-      </c>
-    </row>
-    <row r="345">
-      <c r="A345" t="s">
-        <v>375</v>
-      </c>
-      <c r="B345" t="n">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="346">
-      <c r="A346" t="s">
-        <v>376</v>
-      </c>
-      <c r="B346" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="347">
-      <c r="A347" t="s">
-        <v>377</v>
-      </c>
-      <c r="B347" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="348">
-      <c r="A348" t="s">
-        <v>378</v>
-      </c>
-      <c r="B348" t="n">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="349">
-      <c r="A349" t="s">
-        <v>379</v>
-      </c>
-      <c r="B349" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="350">
-      <c r="A350" t="s">
-        <v>380</v>
-      </c>
-      <c r="B350" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="351">
-      <c r="A351" t="s">
-        <v>381</v>
-      </c>
-      <c r="B351" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="352">
-      <c r="A352" t="s">
-        <v>382</v>
-      </c>
-      <c r="B352" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="353">
-      <c r="A353" t="s">
-        <v>383</v>
-      </c>
-      <c r="B353" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="354">
-      <c r="A354" t="s">
-        <v>384</v>
-      </c>
-      <c r="B354" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="355">
-      <c r="A355" t="s">
-        <v>385</v>
-      </c>
-      <c r="B355" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="356">
-      <c r="A356" t="s">
-        <v>386</v>
-      </c>
-      <c r="B356" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="357">
-      <c r="A357" t="s">
-        <v>387</v>
-      </c>
-      <c r="B357" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="358">
-      <c r="A358" t="s">
-        <v>388</v>
-      </c>
-      <c r="B358" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="359">
-      <c r="A359" t="s">
-        <v>389</v>
-      </c>
-      <c r="B359" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="360">
-      <c r="A360" t="s">
-        <v>390</v>
-      </c>
-      <c r="B360" t="n">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="361">
-      <c r="A361" t="s">
-        <v>391</v>
-      </c>
-      <c r="B361" t="n">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="362">
-      <c r="A362" t="s">
-        <v>392</v>
-      </c>
-      <c r="B362" t="n">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="363">
-      <c r="A363" t="s">
-        <v>393</v>
-      </c>
-      <c r="B363" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="364">
-      <c r="A364" t="s">
-        <v>394</v>
-      </c>
-      <c r="B364" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="365">
-      <c r="A365" t="s">
-        <v>395</v>
-      </c>
-      <c r="B365" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="366">
-      <c r="A366" t="s">
-        <v>396</v>
-      </c>
-      <c r="B366" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="367">
-      <c r="A367" t="s">
-        <v>397</v>
-      </c>
-      <c r="B367" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="368">
-      <c r="A368" t="s">
-        <v>398</v>
-      </c>
-      <c r="B368" t="n">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="369">
-      <c r="A369" t="s">
-        <v>399</v>
-      </c>
-      <c r="B369" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="370">
-      <c r="A370" t="s">
-        <v>400</v>
-      </c>
-      <c r="B370" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="371">
-      <c r="A371" t="s">
-        <v>401</v>
-      </c>
-      <c r="B371" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="372">
-      <c r="A372" t="s">
-        <v>402</v>
-      </c>
-      <c r="B372" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="373">
-      <c r="A373" t="s">
-        <v>403</v>
-      </c>
-      <c r="B373" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="374">
-      <c r="A374" t="s">
-        <v>404</v>
-      </c>
-      <c r="B374" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="375">
-      <c r="A375" t="s">
-        <v>405</v>
-      </c>
-      <c r="B375" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="376">
-      <c r="A376" t="s">
-        <v>406</v>
-      </c>
-      <c r="B376" t="n">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="377">
-      <c r="A377" t="s">
-        <v>407</v>
-      </c>
-      <c r="B377" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="378">
-      <c r="A378" t="s">
-        <v>408</v>
-      </c>
-      <c r="B378" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="379">
-      <c r="A379" t="s">
-        <v>409</v>
-      </c>
-      <c r="B379" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="380">
-      <c r="A380" t="s">
-        <v>410</v>
-      </c>
-      <c r="B380" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="381">
-      <c r="A381" t="s">
-        <v>411</v>
-      </c>
-      <c r="B381" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="382">
-      <c r="A382" t="s">
-        <v>412</v>
-      </c>
-      <c r="B382" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="383">
-      <c r="A383" t="s">
-        <v>413</v>
-      </c>
-      <c r="B383" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="384">
-      <c r="A384" t="s">
-        <v>414</v>
-      </c>
-      <c r="B384" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="385">
-      <c r="A385" t="s">
-        <v>415</v>
-      </c>
-      <c r="B385" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="386">
-      <c r="A386" t="s">
-        <v>416</v>
-      </c>
-      <c r="B386" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="387">
-      <c r="A387" t="s">
-        <v>417</v>
-      </c>
-      <c r="B387" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="388">
-      <c r="A388" t="s">
-        <v>418</v>
-      </c>
-      <c r="B388" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="389">
-      <c r="A389" t="s">
-        <v>419</v>
-      </c>
-      <c r="B389" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="390">
-      <c r="A390" t="s">
-        <v>420</v>
-      </c>
-      <c r="B390" t="n">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="391">
-      <c r="A391" t="s">
-        <v>421</v>
-      </c>
-      <c r="B391" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="392">
-      <c r="A392" t="s">
-        <v>422</v>
-      </c>
-      <c r="B392" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="393">
-      <c r="A393" t="s">
-        <v>423</v>
-      </c>
-      <c r="B393" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="394">
-      <c r="A394" t="s">
-        <v>424</v>
-      </c>
-      <c r="B394" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="395">
-      <c r="A395" t="s">
-        <v>425</v>
-      </c>
-      <c r="B395" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="396">
-      <c r="A396" t="s">
-        <v>426</v>
-      </c>
-      <c r="B396" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="397">
-      <c r="A397" t="s">
-        <v>427</v>
-      </c>
-      <c r="B397" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="398">
-      <c r="A398" t="s">
-        <v>428</v>
-      </c>
-      <c r="B398" t="n">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="399">
-      <c r="A399" t="s">
-        <v>429</v>
-      </c>
-      <c r="B399" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="400">
-      <c r="A400" t="s">
-        <v>430</v>
-      </c>
-      <c r="B400" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="401">
-      <c r="A401" t="s">
-        <v>431</v>
-      </c>
-      <c r="B401" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="402">
-      <c r="A402" t="s">
-        <v>432</v>
-      </c>
-      <c r="B402" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="403">
-      <c r="A403" t="s">
-        <v>433</v>
-      </c>
-      <c r="B403" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="404">
-      <c r="A404" t="s">
-        <v>434</v>
-      </c>
-      <c r="B404" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="405">
-      <c r="A405" t="s">
-        <v>435</v>
-      </c>
-      <c r="B405" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="406">
-      <c r="A406" t="s">
-        <v>436</v>
-      </c>
-      <c r="B406" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="407">
-      <c r="A407" t="s">
-        <v>437</v>
-      </c>
-      <c r="B407" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="408">
-      <c r="A408" t="s">
-        <v>438</v>
-      </c>
-      <c r="B408" t="n">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="409">
-      <c r="A409" t="s">
-        <v>439</v>
-      </c>
-      <c r="B409" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="410">
-      <c r="A410" t="s">
-        <v>440</v>
-      </c>
-      <c r="B410" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="411">
-      <c r="A411" t="s">
-        <v>441</v>
-      </c>
-      <c r="B411" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="412">
-      <c r="A412" t="s">
-        <v>442</v>
-      </c>
-      <c r="B412" t="n">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="413">
-      <c r="A413" t="s">
-        <v>443</v>
-      </c>
-      <c r="B413" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="414">
-      <c r="A414" t="s">
-        <v>444</v>
-      </c>
-      <c r="B414" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="415">
-      <c r="A415" t="s">
-        <v>445</v>
-      </c>
-      <c r="B415" t="n">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="416">
-      <c r="A416" t="s">
-        <v>446</v>
-      </c>
-      <c r="B416" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="417">
-      <c r="A417" t="s">
-        <v>447</v>
-      </c>
-      <c r="B417" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="418">
-      <c r="A418" t="s">
-        <v>448</v>
-      </c>
-      <c r="B418" t="n">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="419">
-      <c r="A419" t="s">
-        <v>449</v>
-      </c>
-      <c r="B419" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="420">
-      <c r="A420" t="s">
-        <v>450</v>
-      </c>
-      <c r="B420" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="421">
-      <c r="A421" t="s">
-        <v>451</v>
-      </c>
-      <c r="B421" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
   </sheetData>
